--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,6 +523,21 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -534,17 +552,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -555,14 +573,14 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les soldes au 30 avril 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
+          <t>Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-1 a été ajoutée dans le tableau des échéances contractuelles des actifs financiers au 30 avril 2025.
-Cette note précise l'impact de l'acquisition de CWB sur les résultats consolidés de la Banque, ce qui est crucial pour comprendre les variations des soldes financiers. L'acquisition d'une entité peut avoir des implications significatives sur les ratios financiers et la gestion des risques, notamment en ce qui concerne les exigences de fonds propres selon Bâle III et les directives du BSIF.
-Il s'agit d'une divulgation importante qui pourrait affecter l'analyse des risques et la stratégie de gestion de capital. L'analyste devrait confirmer l'intégration de ces informations dans les autres sections pertinentes du rapport et évaluer l'impact sur les ratios prudentiels.</t>
+          <t>L'indicateur "Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux" a été ajouté dans le tableau de gestion des risques au T2 2025, alors qu'il n'était pas présent au T1 2025.
+Cet ajout reflète une attention accrue aux risques liés aux politiques commerciales internationales, qui peuvent avoir un impact significatif sur les opérations bancaires, notamment en ce qui concerne le financement du commerce et les expositions transfrontalières. Les incertitudes dans les politiques tarifaires peuvent affecter la stabilité des flux commerciaux et, par conséquent, la qualité des actifs bancaires.
+Il s'agit d'une mise à jour structurelle importante qui pourrait indiquer un changement dans l'évaluation des risques par l'institution. L'analyste devrait confirmer que cette nouvelle divulgation est alignée avec les autres sections du rapport sur les risques et évaluer si des mesures d'atténuation spécifiques ont été mises en place.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -571,6 +589,21 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T22:59:57.219754+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -585,43 +618,62 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Les montants remboursables sur demande sont considérés comme étant sans échéance spécifique.</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux</t>
+          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les soldes au 30 avril 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux" a été ajouté dans le tableau de gestion des risques au T2 2025, alors qu'il n'était pas présent au T1 2025.
-Cet ajout reflète une attention accrue aux risques liés aux politiques commerciales internationales, qui peuvent avoir un impact significatif sur les opérations bancaires, notamment en ce qui concerne le financement du commerce et les expositions transfrontalières. Les incertitudes et les hausses potentielles des droits de douane peuvent affecter la rentabilité des entreprises clientes et, par conséquent, le risque de crédit pour la banque.
-Il s'agit d'une mise à jour structurelle importante qui pourrait indiquer un changement dans l'évaluation des risques par la banque. L'analyste devrait confirmer que cette nouvelle divulgation est alignée avec les autres sections du rapport sur les risques et évaluer si des mesures d'atténuation supplémentaires sont nécessaires.</t>
+          <t>La note de bas de page n°1 a subi une révision significative dans le tableau des échéances contractuelles des actifs financiers. Initialement, elle indiquait que les montants remboursables sur demande étaient considérés comme étant sans échéance spécifique. Désormais, elle informe sur l'acquisition de CWB par la Banque et l'impact de cette acquisition sur les soldes au 30 avril 2025.
+Ce changement a un impact structurel important car il introduit une nouvelle information concernant une acquisition majeure, ce qui peut affecter la perception des risques et des actifs financiers consolidés. Bien que cela ne modifie pas directement les ratios prudentiels, cela peut influencer l'analyse des risques et la compréhension des résultats financiers consolidés.
+Il s'agit d'une divulgation nouvelle et significative. L'analyste devrait investiguer l'impact de cette acquisition sur les autres sections du rapport financier et s'assurer que toutes les implications sont correctement intégrées et divulguées.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T23:00:21.135481+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -663,16 +715,31 @@
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Risques émergents – Droits de douane sur les importations" a été retiré du tableau de gestion des risques au T2 2025, alors qu'il était présent au T1 2025.
-Cette suppression semble être compensée par l'ajout d'un indicateur plus détaillé et élargi qui couvre non seulement les droits de douane mais aussi les restrictions commerciales. Cela peut indiquer une réévaluation des risques par la banque, prenant en compte un éventail plus large de facteurs économiques et politiques qui pourraient influencer les opérations bancaires.
-Il s'agit d'une mise à jour structurelle qui pourrait refléter un ajustement dans la stratégie de gestion des risques. L'analyste devrait vérifier que cette suppression est bien justifiée par l'évolution des risques et s'assurer que toutes les implications potentielles sont bien couvertes dans le rapport.</t>
+Ce retrait pourrait indiquer une réévaluation ou une redéfinition des risques liés aux droits de douane, potentiellement en réponse à des changements dans l'environnement commercial mondial. La suppression de cet indicateur pourrait également refléter une consolidation des risques sous une nouvelle catégorie plus large, comme le suggère l'ajout d'un nouvel indicateur plus détaillé.
+Il est recommandé que l'analyste vérifie si cette suppression est compensée par d'autres divulgations dans le rapport et si elle reflète un changement dans la méthodologie d'évaluation des risques de l'institution.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T23:00:43.684353+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -714,16 +781,31 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 47" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout peut indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui pourrait avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III. L'ajout de cette série pourrait également refléter une stratégie de financement ou de gestion du capital visant à optimiser le coût du capital ou à répondre à des besoins spécifiques de liquidité.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette nouvelle série est correctement intégrée dans les calculs de fonds propres et vérifier si des divulgations supplémentaires sont nécessaires pour les parties prenantes.</t>
+Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III. L'ajout de cette série pourrait également refléter une stratégie de financement ou de gestion du capital.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et s'assurer que les informations sont cohérentes avec les autres divulgations financières.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T22:59:49.607733+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -765,16 +847,19 @@
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 49" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
-L'ajout de cette série pourrait signaler une nouvelle émission d'actions privilégiées, ce qui est pertinent pour la gestion des fonds propres de la banque. Les actions privilégiées jouent un rôle clé dans le renforcement des ratios de fonds propres, en particulier dans le contexte des exigences de Bâle III et des lignes directrices du BSIF. Cela pourrait également indiquer une réponse stratégique à des conditions de marché ou à des besoins de financement spécifiques.
-Il s'agit d'une mise à jour structurelle significative. L'analyste devrait s'assurer que cette nouvelle série est correctement reflétée dans les rapports financiers et évaluer l'impact potentiel sur les ratios de fonds propres.</t>
+L'ajout de cette série pourrait signaler une nouvelle émission d'actions privilégiées, ce qui est pertinent pour la gestion des fonds propres de la banque. Les actions privilégiées contribuent au renforcement des fonds propres de catégorie 1, en ligne avec les exigences de Bâle III et les lignes directrices du BSIF. Cela peut également indiquer une stratégie de diversification des sources de financement.
+Il s'agit d'une mise à jour structurelle significative. L'analyste devrait vérifier l'émission de cette nouvelle série et s'assurer que les valeurs sont correctement intégrées dans les rapports financiers.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -816,16 +901,19 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 32" a été retiré du tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était présent au T1 2025.
-La suppression de cette série pourrait indiquer le rachat ou l'annulation de cette tranche d'actions privilégiées, ce qui pourrait avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour satisfaire aux exigences de fonds propres de catégorie 1 selon Bâle III. La disparition de cette série pourrait refléter une stratégie de gestion du capital visant à réduire le coût du capital ou à ajuster la structure des fonds propres en réponse à des conditions de marché.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier les raisons de cette suppression et s'assurer que les impacts sur les ratios de fonds propres sont correctement évalués et divulgués.</t>
+La suppression de cette série pourrait indiquer le rachat ou l'annulation de cette tranche d'actions privilégiées, ce qui peut affecter la composition des fonds propres de la banque. Les actions privilégiées jouent un rôle crucial dans le calcul des ratios de fonds propres de catégorie 1, conformément aux normes de Bâle III. Ce changement pourrait également refléter une réorganisation stratégique du capital.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer la raison de cette suppression et s'assurer que cela est correctement reflété dans les autres sections du rapport financier.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -835,17 +923,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -860,23 +948,26 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>(4) Les ratios au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
+          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°4 a été supprimée dans le tableau des exigences réglementaires de ratios des fonds propres, de levier et TLAC au T2 2025. Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
-L'absence de cette note dans le rapport actuel pourrait indiquer que l'impact du rachat d'actions privilégiées n'est plus pertinent pour les ratios présentés au 30 avril 2025. Cela pourrait être dû à l'expiration de l'effet de ce rachat sur les calculs des ratios ou à une révision de la méthodologie de calcul qui ne nécessite plus cette mention. Selon les lignes directrices du BSIF, toute modification dans la méthodologie de calcul des ratios doit être clairement divulguée pour assurer la transparence et la conformité réglementaire.
-Il s'agit d'un changement structurel potentiel qui pourrait affecter la compréhension des ratios par les parties prenantes. L'analyste devrait confirmer si cette suppression est due à une mise à jour méthodologique ou à une autre raison, et s'assurer que les divulgations restent conformes aux exigences réglementaires.</t>
+          <t>La note de bas de page n°3 a été supprimée dans le tableau de gestion du capital réglementaire, du ratio de levier et du TLAC entre le T1 2025 et le T2 2025. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
+L'impact de cette suppression est principalement structurel. La note fournissait une information contextuelle importante sur les ajustements spécifiques apportés aux données financières du trimestre précédent. En l'absence de cette note, il pourrait y avoir une ambiguïté quant à savoir si des ajustements similaires ont été effectués pour le trimestre en cours ou si le rachat d'actions n'a plus d'impact pertinent sur les données présentées.
+Il s'agit d'une mise à jour structurelle. L'analyste devrait confirmer que l'absence de cette note n'affecte pas la compréhension des ajustements de capital par les utilisateurs finaux. Une vérification de la cohérence avec d'autres documents de divulgation serait également recommandée pour s'assurer que toutes les informations pertinentes sont correctement communiquées.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -886,17 +977,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -906,28 +997,31 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>(4) Les ratios au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°3 a été ajoutée dans le tableau de gestion du capital au T2 2025. Cette note précise que la variation du risque opérationnel est liée à l'inclusion de CWB, calculée selon l'approche standardisée, en conformité avec l'approche de la Banque.
-Cette information est cruciale car elle indique un changement potentiel dans la composition du risque opérationnel, ce qui pourrait avoir des implications sur les ratios de capital réglementaire. L'approche standardisée est souvent utilisée pour assurer la conformité avec les exigences de Bâle III, qui impose des normes strictes pour le calcul des actifs pondérés en fonction des risques.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette inclusion est correctement intégrée dans les autres sections du rapport et qu'elle ne reflète pas un changement de méthodologie non documenté. Une vérification de la cohérence avec les autres divulgations de risque est recommandée.</t>
+          <t>La note de bas de page n°4 a été supprimée dans le tableau des exigences réglementaires de ratios des fonds propres, de levier et TLAC au T2 2025.
+Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025. La suppression de cette note pourrait indiquer que l'impact de ce rachat n'est plus pertinent pour les ratios actuels ou que l'information a été intégrée ailleurs dans le rapport. Cela pourrait avoir des implications sur la transparence des divulgations financières, notamment en ce qui concerne la conformité avec les exigences de Bâle III et les lignes directrices du BSIF.
+Il s'agit d'une mise à jour potentiellement significative qui pourrait affecter la compréhension des ajustements de capital. L'analyste devrait confirmer si cette information est redondante ou si elle a été déplacée, et s'assurer que la suppression n'affecte pas la clarté des divulgations réglementaires.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -937,22 +1031,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -963,22 +1057,37 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet ajout reflète une opération spécifique liée à l'acquisition de CWB, ce qui n'était pas mentionné dans le trimestre précédent.
-L'impact de cet ajout est principalement structurel, car il indique une transaction significative qui affecte les fonds propres de catégorie 1. Bien que cela ne soit pas directement lié à une exigence réglementaire comme Bâle III, cela peut influencer la perception des investisseurs et des régulateurs sur la solidité financière de l'institution.
-Il s'agit d'une mise à jour ordinaire qui reflète une transaction d'entreprise. L'analyste devrait confirmer que cette émission est correctement intégrée dans les calculs des fonds propres et que toutes les implications comptables et réglementaires sont bien prises en compte.</t>
+          <t>La note de bas de page n°3 a été ajoutée dans le tableau de gestion du capital au T2 2025. Cette note précise que la variation du risque opérationnel est liée à l'inclusion de CWB, calculée selon l'approche standardisée.
+Cette information est significative car elle indique un changement dans la composition du risque opérationnel de la banque, potentiellement en raison d'une acquisition ou d'une intégration stratégique. L'approche standardisée mentionnée est conforme aux exigences de Bâle III, qui impose des méthodes spécifiques pour le calcul des risques opérationnels.
+Il s'agit d'une nouvelle divulgation importante. L'analyste devrait confirmer l'impact de cette inclusion sur les ratios prudentiels et s'assurer que cette approche est cohérente avec les autres sections du rapport. Une investigation plus approfondie pourrait être nécessaire pour comprendre les implications stratégiques de cette inclusion.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T23:00:09.438917+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1014,144 +1123,165 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet ajout n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
+L'ajout de cet indicateur reflète une transaction spécifique, à savoir l'acquisition de CWB, qui a un impact direct sur les fonds propres de catégorie 1 sous forme d'actions ordinaires. Cela peut avoir des implications sur les ratios de fonds propres réglementaires, notamment ceux liés aux exigences de Bâle III, car l'émission d'actions ordinaires peut affecter le calcul du ratio CET1.
+Il s'agit d'une mise à jour structurelle importante qui nécessite une attention particulière pour s'assurer que l'impact de cette acquisition est correctement intégré dans les calculs de fonds propres. L'analyste devrait confirmer que cette émission est correctement reflétée dans les autres sections du rapport financier.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T23:00:49.279499+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>Options de remplacement relatives à l'acquisition de CWB</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" apparaît pour la première fois dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Ce nouvel indicateur est lié à l'acquisition de CWB, ce qui n'était pas documenté dans le trimestre précédent.
-L'ajout de cet indicateur a un impact structurel, car il reflète des ajustements spécifiques aux options de remplacement dans le cadre de l'acquisition. Bien que cela ne soit pas directement lié à des exigences réglementaires comme celles de Bâle III, cela peut affecter la structure des fonds propres et la perception des parties prenantes.
-Il s'agit d'une mise à jour ordinaire liée à une transaction d'entreprise. L'analyste devrait vérifier que ces options de remplacement sont correctement comptabilisées et que leur impact sur les fonds propres est bien compris et communiqué.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Portefeuille d’actifs liquides (1)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" apparaît dans le tableau actuel pour le semestre terminé le 30 avril 2025, mais était absent dans le trimestre précédent.
+Cet ajout est significatif car il indique que des options de remplacement ont été émises dans le cadre de l'acquisition de CWB. Cela peut influencer la structure du capital et les calculs des fonds propres, en particulier si ces options sont convertibles en actions ordinaires, ce qui pourrait affecter le ratio CET1 et d'autres mesures de fonds propres réglementaires.
+Cette nouvelle divulgation est structurante et nécessite une vérification approfondie pour s'assurer que toutes les implications de cette transaction sont correctement intégrées dans les rapports financiers. L'analyste devrait examiner les détails de l'acquisition pour évaluer l'impact complet sur les fonds propres.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Actifs liquides – Au 31 janvier 2025</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>L'indicateur "Actifs liquides – Au 31 janvier 2025" a été retiré du tableau du portefeuille d'actifs liquides dans le rapport du trimestre actuel. Cet indicateur servait à fournir une référence temporelle pour les données d'actifs liquides à une date spécifique, soit le 31 janvier 2025.
-L'impact de cette suppression est principalement cosmétique, car elle ne modifie pas la méthodologie de calcul ou la divulgation des actifs liquides eux-mêmes. Les exigences réglementaires telles que Bâle III ou les lignes directrices du BSIF ne sont pas directement affectées par l'absence de cette date spécifique, tant que les données sous-jacentes restent conformes et complètes.
-Il s'agit d'une mise à jour ordinaire qui n'affecte pas la transparence ou la conformité réglementaire. L'analyste devrait simplement confirmer que les données d'actifs liquides sont toujours correctement alignées avec les périodes de référence pertinentes dans le rapport.</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>La note de bas de page n°3 a été supprimée dans le tableau de gestion du capital du rapport actuel. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
-L'absence de cette note dans le rapport actuel pourrait suggérer que l'impact de ce rachat d'actions n'est plus pertinent pour la période de référence actuelle, ou que l'information a été intégrée de manière différente dans le rapport. Cependant, cette suppression n'affecte pas directement les calculs des ratios de fonds propres ou de levier, qui sont régis par les normes de Bâle III et les lignes directrices du BSIF.
-Il s'agit d'une mise à jour ordinaire qui ne nécessite pas d'investigation approfondie, sauf si d'autres sections du rapport indiquent des changements significatifs liés à ce rachat d'actions. L'analyste devrait confirmer que l'absence de cette note n'entraîne pas de confusion dans l'interprétation des données financières.</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°2 a été retirée du tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
+L'absence de cette note dans le rapport actuel pourrait avoir des implications sur la transparence des informations fournies aux investisseurs et aux régulateurs. Le rachat d'actions privilégiées peut affecter les fonds propres de catégorie 1 et, par conséquent, les ratios de fonds propres réglementaires tels que le ratio CET1. Selon les normes de Bâle III et les directives du BSIF, il est crucial de divulguer de manière exhaustive les événements qui influencent la structure du capital.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait investiguer pour comprendre pourquoi cette note a été retirée et s'assurer que toutes les implications du rachat d'actions sont correctement intégrées et divulguées dans le rapport financier actuel.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1161,49 +1291,68 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Les montants remboursables sur demande sont considérés comme étant sans échéance spécifique.</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>La note de bas de page n°2 a été retirée du tableau des variations des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note indiquait que les données au 31 janvier 2025 incluaient le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
-L'impact de cette suppression est principalement cosmétique. La note fournissait une information contextuelle sur un événement spécifique qui a eu lieu après la date de clôture du trimestre précédent. Sa suppression dans le rapport actuel peut être due au fait que l'événement n'est plus pertinent pour la période de reporting actuelle ou qu'il a été intégré dans d'autres sections du rapport.
-Il s'agit d'une mise à jour ordinaire qui n'affecte pas directement les exigences réglementaires ou les ratios prudentiels. L'analyste devrait confirmer que l'information sur le rachat d'actions privilégiées est bien couverte ailleurs dans le rapport si elle est toujours pertinente pour les parties prenantes.</t>
+          <t>La note de bas de page n°2 a été ajoutée dans le tableau des échéances contractuelles des actifs financiers au T2 2025. Cette note indique que les montants remboursables sur demande sont considérés comme étant sans échéance spécifique.
+L'impact de cette note est principalement cosmétique, car elle clarifie une pratique comptable déjà implicite dans la gestion des actifs financiers. Elle n'introduit pas de nouvelle méthodologie ni de changement dans les pratiques de divulgation qui pourraient affecter les ratios prudentiels ou les exigences réglementaires telles que Bâle III ou les directives du BSIF.
+Il s'agit d'une mise à jour ordinaire visant à améliorer la clarté des informations fournies aux utilisateurs des états financiers. L'analyste peut confirmer cette mise à jour sans nécessiter d'investigation supplémentaire.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T23:00:30.092549+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Portefeuille d’actifs liquides (1)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1213,26 +1362,89 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Actifs liquides – Au 31 janvier 2025</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Le changement constaté concerne la suppression d'un tableau entier relatif aux indicateurs des Banques d'importance systémique mondiale (BISM) dans la section de gestion du capital. Ce tableau incluait des indicateurs critiques tels que l'activité transfrontière, la taille, l'interdépendance, la substituabilité/infrastructure financière, et la complexité. Ces indicateurs sont essentiels pour évaluer le risque systémique et la résilience des banques à l'échelle mondiale.
-L'impact réglementaire de cette suppression est significatif. Les BISM sont soumises à des exigences de capital plus strictes en raison de leur potentiel impact sur le système financier global. La suppression de ces indicateurs pourrait indiquer un changement dans la manière dont la banque évalue ou divulgue son statut de BISM, ce qui pourrait avoir des implications sur ses exigences en matière de coussin de fonds propres et de ratios prudentiels. Les références réglementaires pertinentes incluent les directives du Comité de Bâle sur le contrôle bancaire concernant les BISM.
-Il s'agit d'une suppression structurelle importante qui pourrait signaler un changement dans la stratégie de divulgation ou une révision des</t>
+          <t>L'indicateur "Actifs liquides – Au 31 janvier 2025" a été retiré du tableau actuel, alors qu'il était présent dans le tableau précédent. Cet indicateur semble être une référence temporelle spécifique à la date de clôture des actifs liquides pour le 31 janvier 2025.
+L'impact de ce retrait est principalement cosmétique, car il s'agit d'une date de référence qui n'affecte pas directement les calculs ou les ratios prudentiels. Les exigences de Bâle III ou du BSIF ne sont pas directement concernées par la présence ou l'absence de cette date dans le tableau, à moins qu'elle ne soit utilisée pour des comparaisons temporelles spécifiques.
+Il s'agit probablement d'une mise à jour ordinaire pour refléter la période de rapport actuelle. L'analyste devrait confirmer que les autres dates de référence dans le tableau sont correctes et cohérentes avec les périodes de rapport actuelles.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T23:00:14.766149+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:N16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -552,17 +552,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -573,14 +573,14 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux</t>
+          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les soldes au 30 avril 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux" a été ajouté dans le tableau de gestion des risques au T2 2025, alors qu'il n'était pas présent au T1 2025.
-Cet ajout reflète une attention accrue aux risques liés aux politiques commerciales internationales, qui peuvent avoir un impact significatif sur les opérations bancaires, notamment en ce qui concerne le financement du commerce et les expositions transfrontalières. Les incertitudes dans les politiques tarifaires peuvent affecter la stabilité des flux commerciaux et, par conséquent, la qualité des actifs bancaires.
-Il s'agit d'une mise à jour structurelle importante qui pourrait indiquer un changement dans l'évaluation des risques par l'institution. L'analyste devrait confirmer que cette nouvelle divulgation est alignée avec les autres sections du rapport sur les risques et évaluer si des mesures d'atténuation spécifiques ont été mises en place.</t>
+          <t>La note de bas de page n-1 a été ajoutée dans le tableau des échéances contractuelles des actifs financiers au T2 2025.
+Cette note précise l'impact de l'acquisition de CWB par la Banque, en indiquant que les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a affecté les soldes au 30 avril 2025. Cette information est cruciale pour comprendre les variations des soldes financiers présentés dans le tableau, car elle introduit un changement structurel dans la composition des actifs de la Banque.
+Il s'agit d'une divulgation importante qui pourrait avoir des implications sur les ratios prudentiels et la perception des investisseurs quant à la solidité financière de la Banque. L'analyste devrait confirmer l'intégration correcte de ces résultats dans les états financiers consolidés et s'assurer que toutes les implications réglementaires, notamment celles liées aux exigences de Bâle III, sont bien respectées.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -589,21 +589,9 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-18T22:59:57.219754+00:00</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -618,39 +606,35 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Les montants remboursables sur demande sont considérés comme étant sans échéance spécifique.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les soldes au 30 avril 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
+          <t>Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°1 a subi une révision significative dans le tableau des échéances contractuelles des actifs financiers. Initialement, elle indiquait que les montants remboursables sur demande étaient considérés comme étant sans échéance spécifique. Désormais, elle informe sur l'acquisition de CWB par la Banque et l'impact de cette acquisition sur les soldes au 30 avril 2025.
-Ce changement a un impact structurel important car il introduit une nouvelle information concernant une acquisition majeure, ce qui peut affecter la perception des risques et des actifs financiers consolidés. Bien que cela ne modifie pas directement les ratios prudentiels, cela peut influencer l'analyse des risques et la compréhension des résultats financiers consolidés.
-Il s'agit d'une divulgation nouvelle et significative. L'analyste devrait investiguer l'impact de cette acquisition sur les autres sections du rapport financier et s'assurer que toutes les implications sont correctement intégrées et divulguées.</t>
+          <t>L'indicateur "Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux" a été ajouté dans le tableau de gestion des risques au T2 2025. Cet ajout remplace l'indicateur précédent qui portait sur les droits de douane sur les importations, en élargissant le champ pour inclure l'incertitude et les restrictions commerciales.
+Ce changement reflète une mise à jour des risques émergents liés aux échanges commerciaux, qui peuvent avoir un impact significatif sur les opérations bancaires internationales et la gestion des risques de crédit. Les incertitudes commerciales peuvent affecter les prévisions économiques et les stratégies de couverture des risques, ce qui est crucial pour les institutions financières.
+Il s'agit d'une mise à jour ordinaire qui reflète l'évolution des conditions économiques mondiales. L'analyste devrait confirmer que cette mise à jour est alignée avec les autres sections du rapport sur les risques et qu'elle est cohérente avec les analyses économiques actuelles.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -659,21 +643,9 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-18T23:00:21.135481+00:00</t>
-        </is>
-      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -714,9 +686,9 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risques émergents – Droits de douane sur les importations" a été retiré du tableau de gestion des risques au T2 2025, alors qu'il était présent au T1 2025.
-Ce retrait pourrait indiquer une réévaluation ou une redéfinition des risques liés aux droits de douane, potentiellement en réponse à des changements dans l'environnement commercial mondial. La suppression de cet indicateur pourrait également refléter une consolidation des risques sous une nouvelle catégorie plus large, comme le suggère l'ajout d'un nouvel indicateur plus détaillé.
-Il est recommandé que l'analyste vérifie si cette suppression est compensée par d'autres divulgations dans le rapport et si elle reflète un changement dans la méthodologie d'évaluation des risques de l'institution.</t>
+          <t>L'indicateur "Risques émergents – Droits de douane sur les importations" a été retiré du tableau de gestion des risques au T2 2025. Cet indicateur a été remplacé par un nouveau qui couvre un champ plus large incluant l'incertitude et les restrictions commerciales.
+La suppression de cet indicateur spécifique peut refléter un changement dans la manière dont la banque évalue et communique les risques liés aux échanges commerciaux. Cela peut avoir des implications sur la gestion des risques de crédit et la planification stratégique, car les droits de douane et les restrictions commerciales peuvent influencer les flux commerciaux et les relations économiques internationales.
+Il s'agit d'une mise à jour ordinaire qui s'inscrit dans l'évolution des pratiques de gestion des risques. L'analyste devrait vérifier que cette suppression est bien documentée et que les nouvelles informations fournies sont cohérentes avec les autres analyses de risques du rapport.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -725,21 +697,9 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-18T23:00:43.684353+00:00</t>
-        </is>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -781,8 +741,8 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 47" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III. L'ajout de cette série pourrait également refléter une stratégie de financement ou de gestion du capital.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et s'assurer que les informations sont cohérentes avec les autres divulgations financières.</t>
+Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III et aux lignes directrices du BSIF.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et évaluer son impact sur les ratios de fonds propres.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -803,7 +763,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-18T22:59:49.607733+00:00</t>
+          <t>2026-04-19T00:12:24.935014+00:00</t>
         </is>
       </c>
     </row>
@@ -847,8 +807,8 @@
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 49" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
-L'ajout de cette série pourrait signaler une nouvelle émission d'actions privilégiées, ce qui est pertinent pour la gestion des fonds propres de la banque. Les actions privilégiées contribuent au renforcement des fonds propres de catégorie 1, en ligne avec les exigences de Bâle III et les lignes directrices du BSIF. Cela peut également indiquer une stratégie de diversification des sources de financement.
-Il s'agit d'une mise à jour structurelle significative. L'analyste devrait vérifier l'émission de cette nouvelle série et s'assurer que les valeurs sont correctement intégrées dans les rapports financiers.</t>
+Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III et aux lignes directrices du BSIF.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et évaluer son impact sur les ratios de fonds propres.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -901,8 +861,8 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 32" a été retiré du tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était présent au T1 2025.
-La suppression de cette série pourrait indiquer le rachat ou l'annulation de cette tranche d'actions privilégiées, ce qui peut affecter la composition des fonds propres de la banque. Les actions privilégiées jouent un rôle crucial dans le calcul des ratios de fonds propres de catégorie 1, conformément aux normes de Bâle III. Ce changement pourrait également refléter une réorganisation stratégique du capital.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer la raison de cette suppression et s'assurer que cela est correctement reflété dans les autres sections du rapport financier.</t>
+La suppression de cette série pourrait indiquer le rachat ou l'annulation de cette série d'actions privilégiées, ce qui peut affecter la composition des fonds propres de la banque. Les actions privilégiées jouent un rôle clé dans le calcul des ratios de fonds propres de catégorie 1, en lien avec les exigences de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier les raisons de cette suppression et son impact sur les ratios de fonds propres.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -955,8 +915,8 @@
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>La note de bas de page n°3 a été supprimée dans le tableau de gestion du capital réglementaire, du ratio de levier et du TLAC entre le T1 2025 et le T2 2025. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
-L'impact de cette suppression est principalement structurel. La note fournissait une information contextuelle importante sur les ajustements spécifiques apportés aux données financières du trimestre précédent. En l'absence de cette note, il pourrait y avoir une ambiguïté quant à savoir si des ajustements similaires ont été effectués pour le trimestre en cours ou si le rachat d'actions n'a plus d'impact pertinent sur les données présentées.
-Il s'agit d'une mise à jour structurelle. L'analyste devrait confirmer que l'absence de cette note n'affecte pas la compréhension des ajustements de capital par les utilisateurs finaux. Une vérification de la cohérence avec d'autres documents de divulgation serait également recommandée pour s'assurer que toutes les informations pertinentes sont correctement communiquées.</t>
+L'absence de cette note dans le rapport du T2 2025 pourrait avoir un impact sur la compréhension des ajustements de capital pour les parties prenantes. Le rachat d'actions privilégiées peut influencer les fonds propres de catégorie 1 et, par conséquent, les ratios de capital réglementaire. Selon les lignes directrices de Bâle III et les exigences du BSIF, les institutions financières doivent divulguer les événements significatifs qui affectent leur capital réglementaire.
+Il s'agit d'une mise à jour structurelle qui pourrait refléter un changement dans la manière dont les événements postérieurs à la date de clôture sont rapportés. L'analyste devrait confirmer que l'impact de ce rachat est correctement intégré dans les chiffres présentés et que l'absence de la note ne compromet pas la transparence des informations fournies.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1009,8 +969,8 @@
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>La note de bas de page n°4 a été supprimée dans le tableau des exigences réglementaires de ratios des fonds propres, de levier et TLAC au T2 2025.
-Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025. La suppression de cette note pourrait indiquer que l'impact de ce rachat n'est plus pertinent pour les ratios actuels ou que l'information a été intégrée ailleurs dans le rapport. Cela pourrait avoir des implications sur la transparence des divulgations financières, notamment en ce qui concerne la conformité avec les exigences de Bâle III et les lignes directrices du BSIF.
-Il s'agit d'une mise à jour potentiellement significative qui pourrait affecter la compréhension des ajustements de capital. L'analyste devrait confirmer si cette information est redondante ou si elle a été déplacée, et s'assurer que la suppression n'affecte pas la clarté des divulgations réglementaires.</t>
+Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025. La suppression de cette note pourrait signifier que cet événement n'est plus pertinent pour le calcul des ratios actuels ou que l'impact de cet événement a été entièrement intégré dans les chiffres actuels. Cela pourrait avoir des implications sur la transparence des divulgations financières, car les investisseurs et les régulateurs s'attendent à une explication claire des événements significatifs qui influencent les ratios de capital.
+Il s'agit d'une mise à jour potentiellement significative qui pourrait affecter la compréhension des ratios de capital par les parties prenantes. L'analyste devrait confirmer si cette suppression est due à l'intégration complète de l'impact de l'événement ou si d'autres facteurs ont influencé cette décision. Une vérification de la cohérence avec d'autres sections du rapport est recommandée.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1046,7 +1006,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1057,14 +1017,14 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
+          <t>Risque de marché – Acquisitions et cessions</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°3 a été ajoutée dans le tableau de gestion du capital au T2 2025. Cette note précise que la variation du risque opérationnel est liée à l'inclusion de CWB, calculée selon l'approche standardisée.
-Cette information est significative car elle indique un changement dans la composition du risque opérationnel de la banque, potentiellement en raison d'une acquisition ou d'une intégration stratégique. L'approche standardisée mentionnée est conforme aux exigences de Bâle III, qui impose des méthodes spécifiques pour le calcul des risques opérationnels.
-Il s'agit d'une nouvelle divulgation importante. L'analyste devrait confirmer l'impact de cette inclusion sur les ratios prudentiels et s'assurer que cette approche est cohérente avec les autres sections du rapport. Une investigation plus approfondie pourrait être nécessaire pour comprendre les implications stratégiques de cette inclusion.</t>
+          <t>L'indicateur "Risque de marché – Acquisitions et cessions" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout permet de mieux comprendre l'impact des acquisitions et cessions sur le risque de marché, ce qui est crucial pour évaluer les changements dans le profil de risque global de l'institution. Cela pourrait être lié à des changements dans la stratégie d'investissement ou à des exigences accrues de divulgation.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait s'assurer que cette nouvelle information est intégrée de manière cohérente avec les autres indicateurs de risque et qu'elle est conforme aux normes de divulgation.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1085,7 +1045,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-18T23:00:09.438917+00:00</t>
+          <t>2026-04-19T00:12:21.677249+00:00</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1057,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1123,14 +1083,14 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
+          <t>Risque opérationnel – Variation des niveaux de risque</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet ajout n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
-L'ajout de cet indicateur reflète une transaction spécifique, à savoir l'acquisition de CWB, qui a un impact direct sur les fonds propres de catégorie 1 sous forme d'actions ordinaires. Cela peut avoir des implications sur les ratios de fonds propres réglementaires, notamment ceux liés aux exigences de Bâle III, car l'émission d'actions ordinaires peut affecter le calcul du ratio CET1.
-Il s'agit d'une mise à jour structurelle importante qui nécessite une attention particulière pour s'assurer que l'impact de cette acquisition est correctement intégré dans les calculs de fonds propres. L'analyste devrait confirmer que cette émission est correctement reflétée dans les autres sections du rapport financier.</t>
+          <t>L'indicateur "Risque opérationnel – Variation des niveaux de risque" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout permet de suivre plus précisément les variations des niveaux de risque opérationnel, ce qui est essentiel pour la gestion proactive des risques. Cela peut être en réponse à des exigences réglementaires ou à une volonté interne d'améliorer la surveillance des risques opérationnels.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que cette nouvelle mesure est alignée avec les pratiques de gestion des risques opérationnels et qu'elle est conforme aux attentes des régulateurs.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1139,21 +1099,9 @@
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-18T23:00:49.279499+00:00</t>
-        </is>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1163,17 +1111,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1189,14 +1137,14 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Options de remplacement relatives à l'acquisition de CWB</t>
+          <t>Risque opérationnel – Méthode et politique</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" apparaît dans le tableau actuel pour le semestre terminé le 30 avril 2025, mais était absent dans le trimestre précédent.
-Cet ajout est significatif car il indique que des options de remplacement ont été émises dans le cadre de l'acquisition de CWB. Cela peut influencer la structure du capital et les calculs des fonds propres, en particulier si ces options sont convertibles en actions ordinaires, ce qui pourrait affecter le ratio CET1 et d'autres mesures de fonds propres réglementaires.
-Cette nouvelle divulgation est structurante et nécessite une vérification approfondie pour s'assurer que toutes les implications de cette transaction sont correctement intégrées dans les rapports financiers. L'analyste devrait examiner les détails de l'acquisition pour évaluer l'impact complet sur les fonds propres.</t>
+          <t>L'indicateur "Risque opérationnel – Méthode et politique" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout reflète une approche plus détaillée dans la présentation des méthodes et politiques spécifiques au risque opérationnel. Cela peut indiquer une révision des politiques internes ou une réponse à des directives réglementaires exigeant une plus grande transparence dans la gestion des risques opérationnels.
+Il s'agit d'une mise à jour structurelle significative. L'analyste devrait confirmer que cette nouvelle présentation est cohérente avec les autres sections du rapport et qu'elle répond aux attentes des régulateurs.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1217,17 +1165,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1237,20 +1185,20 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°2 a été retirée du tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
-L'absence de cette note dans le rapport actuel pourrait avoir des implications sur la transparence des informations fournies aux investisseurs et aux régulateurs. Le rachat d'actions privilégiées peut affecter les fonds propres de catégorie 1 et, par conséquent, les ratios de fonds propres réglementaires tels que le ratio CET1. Selon les normes de Bâle III et les directives du BSIF, il est crucial de divulguer de manière exhaustive les événements qui influencent la structure du capital.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait investiguer pour comprendre pourquoi cette note a été retirée et s'assurer que toutes les implications du rachat d'actions sont correctement intégrées et divulguées dans le rapport financier actuel.</t>
+          <t>La note de bas de page n-3 a été ajoutée dans le tableau de gestion du capital au T2 2025.
+Cette note précise que la variation du risque opérationnel est attribuée à l'inclusion de CWB, calculée selon l'approche standardisée. Cela indique un changement dans la composition du risque opérationnel, potentiellement lié à une acquisition ou à une intégration stratégique. Cette information est cruciale pour comprendre les ajustements dans le profil de risque de l'institution.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette inclusion est correctement reflétée dans les autres sections du rapport et qu'elle est conforme aux normes de divulgation et aux exigences réglementaires en matière de gestion des risques.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1264,187 +1212,403 @@
       <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet ajout reflète une opération spécifique liée à l'acquisition de CWB, ce qui n'était pas présent dans le trimestre précédent.
+L'ajout de cet indicateur est significatif car il met en lumière une transaction importante qui peut avoir un impact sur la structure du capital de la banque. Les émissions d'actions dans le cadre d'acquisitions peuvent affecter les ratios de fonds propres, qui sont des mesures clés suivies par les régulateurs tels que le BSIF dans le cadre des exigences de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette émission est correctement intégrée dans les calculs des fonds propres et que les impacts sur les ratios prudentiels sont bien compris.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19T00:12:11.271698+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Options de remplacement relatives à l'acquisition de CWB</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet ajout est lié à l'acquisition de CWB et reflète des options de remplacement qui n'étaient pas présentes dans le trimestre précédent.
+Cet ajout est pertinent car il indique des ajustements spécifiques dans la structure du capital en raison de l'acquisition. Les options de remplacement peuvent influencer la composition des fonds propres et, par conséquent, les ratios de capital réglementaires. Ces ajustements doivent être conformes aux exigences de divulgation et de calcul des fonds propres selon les normes de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que ces options sont correctement comptabilisées et que leur impact sur les ratios de fonds propres est bien évalué.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°2 a été supprimée dans le tableau des variations des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note faisait référence à l'impact du rachat d'actions privilégiées série 32 effectué le 17 février 2025, qui était pertinent pour le trimestre précédent.
+L'absence de cette note dans le rapport actuel pourrait indiquer que l'impact de ce rachat n'est plus pertinent pour la période actuelle ou que l'information a été intégrée ailleurs dans le rapport. Les rachats d'actions privilégiées peuvent affecter les fonds propres de catégorie 1 et, par conséquent, les ratios de capital réglementaires, qui sont surveillés de près par les régulateurs comme le BSIF dans le cadre des exigences de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que l'impact de ce rachat est correctement reflété dans les calculs des fonds propres pour la période actuelle et que les ratios prudentiels sont toujours conformes aux exigences réglementaires.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Portefeuille d’actifs liquides (1)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Les montants remboursables sur demande sont considérés comme étant sans échéance spécifique.</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>La note de bas de page n°2 a été ajoutée dans le tableau des échéances contractuelles des actifs financiers au T2 2025. Cette note indique que les montants remboursables sur demande sont considérés comme étant sans échéance spécifique.
-L'impact de cette note est principalement cosmétique, car elle clarifie une pratique comptable déjà implicite dans la gestion des actifs financiers. Elle n'introduit pas de nouvelle méthodologie ni de changement dans les pratiques de divulgation qui pourraient affecter les ratios prudentiels ou les exigences réglementaires telles que Bâle III ou les directives du BSIF.
-Il s'agit d'une mise à jour ordinaire visant à améliorer la clarté des informations fournies aux utilisateurs des états financiers. L'analyste peut confirmer cette mise à jour sans nécessiter d'investigation supplémentaire.</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Au 30 avril 2025</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Un nouvel en-tête de date 'Au 30 avril 2025' a été ajouté dans le tableau actuel. Cet en-tête semble être une simple mise à jour de la période de référence pour les données présentées dans le tableau des actifs liquides. Il est courant que les rapports financiers incluent des en-têtes de date pour indiquer la période couverte par les données.
+L'ajout de cet en-tête n'a pas d'impact direct sur les ratios prudentiels ou les exigences réglementaires, car il ne modifie pas la méthodologie de calcul ou la nature des indicateurs présentés. Il s'agit simplement d'une mise à jour de la période de référence, ce qui est une pratique standard dans les rapports financiers.
+Cet ajout est une mise à jour ordinaire et ne nécessite pas d'action particulière de la part de l'analyste. Il est recommandé de vérifier que les données associées à cette nouvelle période sont cohérentes avec les autres informations du rapport.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Validé</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>analyst</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T23:00:30.092549+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-19T00:12:55.573736+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Portefeuille d’actifs liquides (1)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Actifs liquides – Au 31 janvier 2025</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>L'indicateur "Actifs liquides – Au 31 janvier 2025" a été retiré du tableau actuel, alors qu'il était présent dans le tableau précédent. Cet indicateur semble être une référence temporelle spécifique à la date de clôture des actifs liquides pour le 31 janvier 2025.
-L'impact de ce retrait est principalement cosmétique, car il s'agit d'une date de référence qui n'affecte pas directement les calculs ou les ratios prudentiels. Les exigences de Bâle III ou du BSIF ne sont pas directement concernées par la présence ou l'absence de cette date dans le tableau, à moins qu'elle ne soit utilisée pour des comparaisons temporelles spécifiques.
-Il s'agit probablement d'une mise à jour ordinaire pour refléter la période de rapport actuelle. L'analyste devrait confirmer que les autres dates de référence dans le tableau sont correctes et cohérentes avec les périodes de rapport actuelles.</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>L'en-tête de date 'Actifs liquides – Au 31 janvier 2025' a été supprimé du tableau précédent. Cette suppression semble être une mise à jour de la période de référence pour les données présentées dans le tableau des actifs liquides. Les en-têtes de date sont souvent utilisés pour indiquer la période couverte par les données dans les rapports financiers.
+La suppression de cet en-tête n'affecte pas directement les ratios prudentiels ou les exigences réglementaires, car elle ne modifie pas la méthodologie de calcul ou la nature des indicateurs présentés. Il s'agit simplement d'une mise à jour de la période de référence, ce qui est une pratique courante dans les rapports financiers.
+Cette suppression est une mise à jour ordinaire et ne nécessite pas d'action particulière de la part de l'analyste. Il est conseillé de s'assurer que les données pour la nouvelle période sont correctement reflétées dans le rapport.</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Autres, y compris les ajustements réglementaires</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>L'indicateur "Autres, y compris les ajustements réglementaires" présent dans le tableau du trimestre terminé le 31 janvier 2025 a été supprimé dans le tableau du semestre terminé le 30 avril 2025. Cette suppression pourrait indiquer une réorganisation ou une clarification des ajustements réglementaires dans le tableau actuel.
+Bien que cet indicateur soit souvent utilisé pour regrouper divers ajustements mineurs, sa suppression pourrait refléter un changement dans la manière dont ces ajustements sont présentés ou calculés. Cela pourrait être lié à une mise à jour méthodologique ou à une simplification des divulgations.
+Il s'agit probablement d'une mise à jour cosmétique ou méthodologique. L'analyste devrait confirmer que les ajustements réglementaires sont toujours correctement reflétés dans d'autres parties du tableau ou du rapport.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Tableau</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Tableau supprimé du trimestre courant.</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T23:00:14.766149+00:00</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:N20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -579,8 +579,8 @@
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>La note de bas de page n-1 a été ajoutée dans le tableau des échéances contractuelles des actifs financiers au T2 2025.
-Cette note précise l'impact de l'acquisition de CWB par la Banque, en indiquant que les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a affecté les soldes au 30 avril 2025. Cette information est cruciale pour comprendre les variations des soldes financiers présentés dans le tableau, car elle introduit un changement structurel dans la composition des actifs de la Banque.
-Il s'agit d'une divulgation importante qui pourrait avoir des implications sur les ratios prudentiels et la perception des investisseurs quant à la solidité financière de la Banque. L'analyste devrait confirmer l'intégration correcte de ces résultats dans les états financiers consolidés et s'assurer que toutes les implications réglementaires, notamment celles liées aux exigences de Bâle III, sont bien respectées.</t>
+Cette note précise l'impact de l'acquisition de CWB par la Banque, en indiquant que les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a affecté les soldes au 30 avril 2025. Cette information est cruciale car elle peut influencer la perception des investisseurs et des régulateurs sur la solidité financière de la Banque, notamment en ce qui concerne les ratios de capital et de liquidité. L'acquisition pourrait également avoir des implications sur les exigences de fonds propres selon les normes de Bâle III, en raison de l'intégration de nouveaux actifs et passifs.
+Il s'agit d'une divulgation importante qui pourrait avoir des implications structurelles sur l'analyse des états financiers de la Banque. L'analyste devrait confirmer l'intégration correcte de cette acquisition dans les autres sections du rapport financier et s'assurer que toutes les implications réglementaires ont été correctement adressées.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -632,9 +632,9 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux" a été ajouté dans le tableau de gestion des risques au T2 2025. Cet ajout remplace l'indicateur précédent qui portait sur les droits de douane sur les importations, en élargissant le champ pour inclure l'incertitude et les restrictions commerciales.
-Ce changement reflète une mise à jour des risques émergents liés aux échanges commerciaux, qui peuvent avoir un impact significatif sur les opérations bancaires internationales et la gestion des risques de crédit. Les incertitudes commerciales peuvent affecter les prévisions économiques et les stratégies de couverture des risques, ce qui est crucial pour les institutions financières.
-Il s'agit d'une mise à jour ordinaire qui reflète l'évolution des conditions économiques mondiales. L'analyste devrait confirmer que cette mise à jour est alignée avec les autres sections du rapport sur les risques et qu'elle est cohérente avec les analyses économiques actuelles.</t>
+          <t>L'indicateur "Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux" a été ajouté dans le tableau de gestion des risques au T2 2025, alors qu'il n'était pas présent au T1 2025.
+Cet ajout reflète une attention accrue aux risques liés aux fluctuations des droits de douane et aux restrictions commerciales, qui peuvent avoir un impact significatif sur les opérations bancaires internationales et la gestion des risques de crédit. Les institutions financières doivent surveiller ces évolutions pour ajuster leurs stratégies de couverture et de gestion des risques, conformément aux lignes directrices prudentielles.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cet ajout est aligné avec les autres sections du rapport sur les risques émergents et évaluer l'impact potentiel sur les stratégies de gestion des risques de l'institution.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -686,9 +686,9 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risques émergents – Droits de douane sur les importations" a été retiré du tableau de gestion des risques au T2 2025. Cet indicateur a été remplacé par un nouveau qui couvre un champ plus large incluant l'incertitude et les restrictions commerciales.
-La suppression de cet indicateur spécifique peut refléter un changement dans la manière dont la banque évalue et communique les risques liés aux échanges commerciaux. Cela peut avoir des implications sur la gestion des risques de crédit et la planification stratégique, car les droits de douane et les restrictions commerciales peuvent influencer les flux commerciaux et les relations économiques internationales.
-Il s'agit d'une mise à jour ordinaire qui s'inscrit dans l'évolution des pratiques de gestion des risques. L'analyste devrait vérifier que cette suppression est bien documentée et que les nouvelles informations fournies sont cohérentes avec les autres analyses de risques du rapport.</t>
+          <t>L'indicateur "Risques émergents – Droits de douane sur les importations" a été retiré du tableau de gestion des risques au T2 2025, alors qu'il était présent au T1 2025.
+Ce retrait peut indiquer un changement dans la focalisation des risques émergents, passant d'une attention spécifique aux droits de douane sur les importations à une perspective plus large incluant les incertitudes et restrictions commerciales. Cela peut refléter une réévaluation des priorités en matière de gestion des risques, en réponse à des évolutions économiques ou politiques récentes.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier si ce retrait est compensé par d'autres indicateurs ou sections du rapport, et évaluer l'impact sur la stratégie globale de gestion des risques de l'institution.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
         <is>
           <t>L'indicateur "Série 47" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
 Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III et aux lignes directrices du BSIF.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et évaluer son impact sur les ratios de fonds propres.</t>
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et s'assurer que les informations sont cohérentes avec les autres divulgations financières.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-19T00:12:24.935014+00:00</t>
+          <t>2026-04-23T18:57:41.194006+00:00</t>
         </is>
       </c>
     </row>
@@ -807,8 +807,8 @@
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 49" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III et aux lignes directrices du BSIF.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et évaluer son impact sur les ratios de fonds propres.</t>
+L'ajout de cette série suggère une nouvelle émission d'actions privilégiées, ce qui peut influencer la composition des fonds propres de la banque. Les actions privilégiées jouent un rôle clé dans le renforcement des ratios de fonds propres, en ligne avec les exigences réglementaires de Bâle III.
+Il s'agit d'une mise à jour structurelle significative. L'analyste devrait vérifier l'exactitude de cette nouvelle émission et son impact sur les ratios de fonds propres.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -861,8 +861,8 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 32" a été retiré du tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était présent au T1 2025.
-La suppression de cette série pourrait indiquer le rachat ou l'annulation de cette série d'actions privilégiées, ce qui peut affecter la composition des fonds propres de la banque. Les actions privilégiées jouent un rôle clé dans le calcul des ratios de fonds propres de catégorie 1, en lien avec les exigences de Bâle III.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier les raisons de cette suppression et son impact sur les ratios de fonds propres.</t>
+La suppression de cette série peut indiquer le rachat ou l'annulation de cette émission d'actions privilégiées, ce qui pourrait affecter la structure du capital de la banque. Les actions privilégiées sont essentielles pour maintenir les ratios de fonds propres requis par Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer la raison de cette suppression et évaluer son impact sur les ratios de fonds propres et la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -914,9 +914,9 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°3 a été supprimée dans le tableau de gestion du capital réglementaire, du ratio de levier et du TLAC entre le T1 2025 et le T2 2025. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
-L'absence de cette note dans le rapport du T2 2025 pourrait avoir un impact sur la compréhension des ajustements de capital pour les parties prenantes. Le rachat d'actions privilégiées peut influencer les fonds propres de catégorie 1 et, par conséquent, les ratios de capital réglementaire. Selon les lignes directrices de Bâle III et les exigences du BSIF, les institutions financières doivent divulguer les événements significatifs qui affectent leur capital réglementaire.
-Il s'agit d'une mise à jour structurelle qui pourrait refléter un changement dans la manière dont les événements postérieurs à la date de clôture sont rapportés. L'analyste devrait confirmer que l'impact de ce rachat est correctement intégré dans les chiffres présentés et que l'absence de la note ne compromet pas la transparence des informations fournies.</t>
+          <t>La note de bas de page n°3 a été supprimée dans le tableau de gestion du capital réglementaire, du ratio de levier et du TLAC. Cette note faisait référence à l'impact du rachat d'actions privilégiées série 32 sur les données au 31 janvier 2025.
+L'absence de cette note dans le rapport actuel pourrait indiquer que l'effet de ce rachat n'est plus pertinent pour la période actuelle ou que l'information a été intégrée ailleurs dans le rapport. Cela pourrait avoir un impact sur la compréhension des ajustements de capital et des ratios de fonds propres, notamment si ces ajustements influencent les calculs de Bâle III ou les exigences du BSIF.
+Il s'agit potentiellement d'une mise à jour structurelle. L'analyste devrait confirmer si l'impact du rachat d'actions a été traité différemment dans le rapport actuel ou s'il est devenu obsolète. Une vérification de la cohérence avec d'autres sections du rapport est recommandée.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -925,9 +925,21 @@
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T18:59:00.240659+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -968,9 +980,9 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°4 a été supprimée dans le tableau des exigences réglementaires de ratios des fonds propres, de levier et TLAC au T2 2025.
-Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025. La suppression de cette note pourrait signifier que cet événement n'est plus pertinent pour le calcul des ratios actuels ou que l'impact de cet événement a été entièrement intégré dans les chiffres actuels. Cela pourrait avoir des implications sur la transparence des divulgations financières, car les investisseurs et les régulateurs s'attendent à une explication claire des événements significatifs qui influencent les ratios de capital.
-Il s'agit d'une mise à jour potentiellement significative qui pourrait affecter la compréhension des ratios de capital par les parties prenantes. L'analyste devrait confirmer si cette suppression est due à l'intégration complète de l'impact de l'événement ou si d'autres facteurs ont influencé cette décision. Une vérification de la cohérence avec d'autres sections du rapport est recommandée.</t>
+          <t>La note de bas de page n°4 a été supprimée dans le tableau des exigences réglementaires de ratios des fonds propres, de levier et TLAC au T2 2025. Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
+L'absence de cette note dans le rapport actuel pourrait avoir un impact sur la transparence des informations fournies aux investisseurs et aux régulateurs. En effet, le rachat d'actions privilégiées peut influencer les ratios de fonds propres, et son omission pourrait masquer des variations importantes dans les calculs des ratios prudentiels. Selon les lignes directrices du BSIF, toute modification significative des éléments de fonds propres doit être clairement divulguée pour assurer la conformité avec les exigences de Bâle III.
+Il s'agit d'une mise à jour potentiellement significative qui pourrait indiquer un changement dans la manière dont les événements postérieurs sont pris en compte dans les calculs des ratios. L'analyste devrait confirmer si cette omission est intentionnelle et si elle est conforme aux pratiques de divulgation actuelles. Une investigation plus approfondie est recommandée pour s'assurer que toutes les informations pertinentes sont correctement communiquées.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1023,8 +1035,8 @@
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Risque de marché – Acquisitions et cessions" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout permet de mieux comprendre l'impact des acquisitions et cessions sur le risque de marché, ce qui est crucial pour évaluer les changements dans le profil de risque global de l'institution. Cela pourrait être lié à des changements dans la stratégie d'investissement ou à des exigences accrues de divulgation.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait s'assurer que cette nouvelle information est intégrée de manière cohérente avec les autres indicateurs de risque et qu'elle est conforme aux normes de divulgation.</t>
+Cet ajout permet de mieux isoler l'impact des acquisitions et cessions sur le risque de marché, ce qui est crucial pour l'évaluation des risques et la planification stratégique. Cela pourrait être lié à des changements dans la structure de l'entreprise ou à des exigences de divulgation accrues.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait s'assurer que cette nouvelle catégorie est justifiée par des changements dans les opérations ou les exigences réglementaires.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1033,21 +1045,9 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:12:21.677249+00:00</t>
-        </is>
-      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1083,14 +1083,14 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Risque opérationnel – Variation des niveaux de risque</t>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risque opérationnel – Variation des niveaux de risque" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout permet de suivre plus précisément les variations des niveaux de risque opérationnel, ce qui est essentiel pour la gestion proactive des risques. Cela peut être en réponse à des exigences réglementaires ou à une volonté interne d'améliorer la surveillance des risques opérationnels.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que cette nouvelle mesure est alignée avec les pratiques de gestion des risques opérationnels et qu'elle est conforme aux attentes des régulateurs.</t>
+          <t>La note de bas de page n-3 a été ajoutée dans le tableau de gestion du capital au T2 2025.
+Cette note précise que la variation du risque opérationnel est attribuée à l'inclusion de CWB, calculée selon l'approche standardisée. Cela indique un changement potentiel dans la manière dont le risque opérationnel est évalué, ce qui pourrait avoir des implications sur les ratios de capital réglementaire et la conformité aux normes de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette inclusion est cohérente avec les autres sections du rapport et vérifier si elle répond à de nouvelles exigences réglementaires.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1137,14 +1137,14 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Risque opérationnel – Méthode et politique</t>
+          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risque opérationnel – Méthode et politique" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout reflète une approche plus détaillée dans la présentation des méthodes et politiques spécifiques au risque opérationnel. Cela peut indiquer une révision des politiques internes ou une réponse à des directives réglementaires exigeant une plus grande transparence dans la gestion des risques opérationnels.
-Il s'agit d'une mise à jour structurelle significative. L'analyste devrait confirmer que cette nouvelle présentation est cohérente avec les autres sections du rapport et qu'elle répond aux attentes des régulateurs.</t>
+          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet indicateur n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
+Cet ajout reflète une opération spécifique d'acquisition, ce qui peut avoir un impact significatif sur la structure du capital de la banque. Les émissions d'actions ordinaires dans le cadre d'acquisitions peuvent affecter les ratios de fonds propres, qui sont des éléments clés pour le respect des exigences réglementaires telles que Bâle III. Cela peut également influencer la perception des investisseurs et des régulateurs quant à la stratégie de croissance de la banque.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette émission est correctement intégrée dans les calculs des fonds propres et que les impacts sur les ratios réglementaires sont bien documentés.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1153,9 +1153,21 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23T18:58:47.043611+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1165,22 +1177,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1191,14 +1203,14 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
+          <t>Options de remplacement relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-3 a été ajoutée dans le tableau de gestion du capital au T2 2025.
-Cette note précise que la variation du risque opérationnel est attribuée à l'inclusion de CWB, calculée selon l'approche standardisée. Cela indique un changement dans la composition du risque opérationnel, potentiellement lié à une acquisition ou à une intégration stratégique. Cette information est cruciale pour comprendre les ajustements dans le profil de risque de l'institution.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette inclusion est correctement reflétée dans les autres sections du rapport et qu'elle est conforme aux normes de divulgation et aux exigences réglementaires en matière de gestion des risques.</t>
+          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet indicateur n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
+Cet ajout est lié à l'acquisition de CWB et concerne les options de remplacement, ce qui peut avoir des implications sur la valorisation des actions et les droits des actionnaires. Les options de remplacement peuvent modifier la structure du capital et influencer les calculs des fonds propres réglementaires, ce qui est crucial pour le respect des normes de Bâle III et des directives du BSIF.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que ces options sont correctement évaluées et intégrées dans les rapports financiers, et que leur impact sur les ratios de fonds propres est bien compris.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1234,25 +1246,25 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet ajout reflète une opération spécifique liée à l'acquisition de CWB, ce qui n'était pas présent dans le trimestre précédent.
-L'ajout de cet indicateur est significatif car il met en lumière une transaction importante qui peut avoir un impact sur la structure du capital de la banque. Les émissions d'actions dans le cadre d'acquisitions peuvent affecter les ratios de fonds propres, qui sont des mesures clés suivies par les régulateurs tels que le BSIF dans le cadre des exigences de Bâle III.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette émission est correctement intégrée dans les calculs des fonds propres et que les impacts sur les ratios prudentiels sont bien compris.</t>
+          <t>La note de bas de page n°2 a été supprimée du tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note était présente dans le trimestre précédent terminé le 31 janvier 2025.
+Cette note précisait que les données incluaient le rachat d’actions privilégiées série 32 effectué le 17 février 2025. La suppression de cette note pourrait indiquer que l'événement de rachat n'est plus pertinent pour la période actuelle ou que son impact a été entièrement intégré dans les chiffres présentés. Cela peut avoir des implications sur la transparence des informations fournies aux investisseurs et aux régulateurs, notamment en ce qui concerne la gestion des fonds propres et le respect des exigences de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que l'impact de ce rachat est correctement reflété dans les autres sections du rapport et que la suppression de la note ne compromet pas la compréhension des changements dans les fonds propres.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1273,342 +1285,138 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-19T00:12:11.271698+00:00</t>
+          <t>2026-04-23T18:58:52.570557+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Portefeuille d’actifs liquides (1)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Actifs liquides – Au 31 janvier 2025</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>L'indicateur "Actifs liquides – Au 31 janvier 2025" a été retiré du tableau actuel, alors qu'il était présent dans le tableau précédent. Cet indicateur servait à fournir une référence temporelle spécifique pour les actifs liquides à une date antérieure, ce qui est une pratique courante pour contextualiser les données financières dans le temps.
+L'impact de cette suppression est principalement cosmétique, car elle ne modifie pas la méthodologie de calcul ou la présentation des actifs liquides eux-mêmes. Cependant, elle peut affecter la comparaison temporelle directe des données si les utilisateurs du rapport s'appuient sur ces dates pour suivre les tendances historiques. Dans le cadre des exigences réglementaires, cette suppression n'a pas d'incidence directe, car les dates de référence ne sont pas des éléments obligatoires de divulgation selon Bâle III ou les lignes directrices du BSIF.
+Il s'agit d'une mise à jour ordinaire visant probablement à simplifier la présentation du tableau. L'analyste devrait confirmer que les autres dates de référence pertinentes sont toujours présentes et que les utilisateurs du rapport ont accès à toutes les informations nécessaires pour une analyse temporelle complète.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23T18:58:56.509411+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Options de remplacement relatives à l'acquisition de CWB</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet ajout est lié à l'acquisition de CWB et reflète des options de remplacement qui n'étaient pas présentes dans le trimestre précédent.
-Cet ajout est pertinent car il indique des ajustements spécifiques dans la structure du capital en raison de l'acquisition. Les options de remplacement peuvent influencer la composition des fonds propres et, par conséquent, les ratios de capital réglementaires. Ces ajustements doivent être conformes aux exigences de divulgation et de calcul des fonds propres selon les normes de Bâle III.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que ces options sont correctement comptabilisées et que leur impact sur les ratios de fonds propres est bien évalué.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>La note de bas de page n°2 a été supprimée dans le tableau des variations des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note faisait référence à l'impact du rachat d'actions privilégiées série 32 effectué le 17 février 2025, qui était pertinent pour le trimestre précédent.
-L'absence de cette note dans le rapport actuel pourrait indiquer que l'impact de ce rachat n'est plus pertinent pour la période actuelle ou que l'information a été intégrée ailleurs dans le rapport. Les rachats d'actions privilégiées peuvent affecter les fonds propres de catégorie 1 et, par conséquent, les ratios de capital réglementaires, qui sont surveillés de près par les régulateurs comme le BSIF dans le cadre des exigences de Bâle III.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que l'impact de ce rachat est correctement reflété dans les calculs des fonds propres pour la période actuelle et que les ratios prudentiels sont toujours conformes aux exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Portefeuille d’actifs liquides (1)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Au 30 avril 2025</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Un nouvel en-tête de date 'Au 30 avril 2025' a été ajouté dans le tableau actuel. Cet en-tête semble être une simple mise à jour de la période de référence pour les données présentées dans le tableau des actifs liquides. Il est courant que les rapports financiers incluent des en-têtes de date pour indiquer la période couverte par les données.
-L'ajout de cet en-tête n'a pas d'impact direct sur les ratios prudentiels ou les exigences réglementaires, car il ne modifie pas la méthodologie de calcul ou la nature des indicateurs présentés. Il s'agit simplement d'une mise à jour de la période de référence, ce qui est une pratique standard dans les rapports financiers.
-Cet ajout est une mise à jour ordinaire et ne nécessite pas d'action particulière de la part de l'analyste. Il est recommandé de vérifier que les données associées à cette nouvelle période sont cohérentes avec les autres informations du rapport.</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Validé</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>analyst</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:12:55.573736+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Portefeuille d’actifs liquides (1)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Actifs liquides – Au 31 janvier 2025</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>L'en-tête de date 'Actifs liquides – Au 31 janvier 2025' a été supprimé du tableau précédent. Cette suppression semble être une mise à jour de la période de référence pour les données présentées dans le tableau des actifs liquides. Les en-têtes de date sont souvent utilisés pour indiquer la période couverte par les données dans les rapports financiers.
-La suppression de cet en-tête n'affecte pas directement les ratios prudentiels ou les exigences réglementaires, car elle ne modifie pas la méthodologie de calcul ou la nature des indicateurs présentés. Il s'agit simplement d'une mise à jour de la période de référence, ce qui est une pratique courante dans les rapports financiers.
-Cette suppression est une mise à jour ordinaire et ne nécessite pas d'action particulière de la part de l'analyste. Il est conseillé de s'assurer que les données pour la nouvelle période sont correctement reflétées dans le rapport.</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Autres, y compris les ajustements réglementaires</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>L'indicateur "Autres, y compris les ajustements réglementaires" présent dans le tableau du trimestre terminé le 31 janvier 2025 a été supprimé dans le tableau du semestre terminé le 30 avril 2025. Cette suppression pourrait indiquer une réorganisation ou une clarification des ajustements réglementaires dans le tableau actuel.
-Bien que cet indicateur soit souvent utilisé pour regrouper divers ajustements mineurs, sa suppression pourrait refléter un changement dans la manière dont ces ajustements sont présentés ou calculés. Cela pourrait être lié à une mise à jour méthodologique ou à une simplification des divulgations.
-Il s'agit probablement d'une mise à jour cosmétique ou méthodologique. L'analyste devrait confirmer que les ajustements réglementaires sont toujours correctement reflétés dans d'autres parties du tableau ou du rapport.</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>Tableau supprimé du trimestre courant.</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23T18:59:06.366153+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:N16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -460,11 +460,10 @@
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,7 +514,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Nouvelle divulgation ?</t>
+          <t>Nouvelle idée ?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -529,11 +528,6 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Validé par</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Validé le</t>
         </is>
@@ -579,8 +573,8 @@
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>La note de bas de page n-1 a été ajoutée dans le tableau des échéances contractuelles des actifs financiers au T2 2025.
-Cette note précise l'impact de l'acquisition de CWB par la Banque, en indiquant que les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a affecté les soldes au 30 avril 2025. Cette information est cruciale car elle peut influencer la perception des investisseurs et des régulateurs sur la solidité financière de la Banque, notamment en ce qui concerne les ratios de capital et de liquidité. L'acquisition pourrait également avoir des implications sur les exigences de fonds propres selon les normes de Bâle III, en raison de l'intégration de nouveaux actifs et passifs.
-Il s'agit d'une divulgation importante qui pourrait avoir des implications structurelles sur l'analyse des états financiers de la Banque. L'analyste devrait confirmer l'intégration correcte de cette acquisition dans les autres sections du rapport financier et s'assurer que toutes les implications réglementaires ont été correctement adressées.</t>
+Cette note précise que la Banque a conclu l'acquisition de CWB le 3 février 2025, et que les résultats de CWB ont été consolidés à partir de cette date, impactant ainsi les soldes au 30 avril 2025. Cette information est cruciale car elle affecte directement la présentation des actifs financiers et pourrait influencer les ratios financiers et les analyses de risque associées.
+Il s'agit d'une divulgation importante liée à une acquisition stratégique. L'analyste devrait confirmer l'intégration correcte des résultats de CWB dans les états financiers consolidés et s'assurer que toutes les implications réglementaires et comptables ont été correctement adressées.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -591,7 +585,6 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -633,19 +626,18 @@
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Risques émergents – Hausse et incertitude des droits de douane et des restrictions sur les échanges commerciaux" a été ajouté dans le tableau de gestion des risques au T2 2025, alors qu'il n'était pas présent au T1 2025.
-Cet ajout reflète une attention accrue aux risques liés aux fluctuations des droits de douane et aux restrictions commerciales, qui peuvent avoir un impact significatif sur les opérations bancaires internationales et la gestion des risques de crédit. Les institutions financières doivent surveiller ces évolutions pour ajuster leurs stratégies de couverture et de gestion des risques, conformément aux lignes directrices prudentielles.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cet ajout est aligné avec les autres sections du rapport sur les risques émergents et évaluer l'impact potentiel sur les stratégies de gestion des risques de l'institution.</t>
+Cet ajout reflète une attention accrue aux risques liés aux fluctuations des droits de douane et aux restrictions commerciales, qui peuvent avoir un impact significatif sur les opérations bancaires internationales et la gestion des risques de crédit. Les institutions financières doivent surveiller ces risques pour se conformer aux exigences réglementaires et maintenir la stabilité financière.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cet ajout est aligné avec les autres sections du rapport sur la gestion des risques et évaluer l'impact potentiel sur les stratégies de gestion des risques de l'institution.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -687,19 +679,18 @@
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Risques émergents – Droits de douane sur les importations" a été retiré du tableau de gestion des risques au T2 2025, alors qu'il était présent au T1 2025.
-Ce retrait peut indiquer un changement dans la focalisation des risques émergents, passant d'une attention spécifique aux droits de douane sur les importations à une perspective plus large incluant les incertitudes et restrictions commerciales. Cela peut refléter une réévaluation des priorités en matière de gestion des risques, en réponse à des évolutions économiques ou politiques récentes.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier si ce retrait est compensé par d'autres indicateurs ou sections du rapport, et évaluer l'impact sur la stratégie globale de gestion des risques de l'institution.</t>
+Ce retrait peut indiquer un changement dans la focalisation des risques émergents, passant d'une attention spécifique aux droits de douane sur les importations à une perspective plus large englobant l'incertitude et les restrictions commerciales. Cela peut refléter une adaptation aux évolutions du contexte économique mondial et aux nouvelles directives réglementaires.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier si ce retrait est compensé par d'autres indicateurs ou sections du rapport et évaluer l'impact sur la communication des risques à l'interne et à l'externe.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -742,30 +733,17 @@
         <is>
           <t>L'indicateur "Série 47" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
 Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III et aux lignes directrices du BSIF.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et s'assurer que les informations sont cohérentes avec les autres divulgations financières.</t>
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et évaluer son impact sur les ratios de fonds propres.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T18:57:41.194006+00:00</t>
-        </is>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -807,19 +785,18 @@
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 49" a été ajouté dans le tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était absent au T1 2025.
-L'ajout de cette série suggère une nouvelle émission d'actions privilégiées, ce qui peut influencer la composition des fonds propres de la banque. Les actions privilégiées jouent un rôle clé dans le renforcement des ratios de fonds propres, en ligne avec les exigences réglementaires de Bâle III.
-Il s'agit d'une mise à jour structurelle significative. L'analyste devrait vérifier l'exactitude de cette nouvelle émission et son impact sur les ratios de fonds propres.</t>
+Cet ajout pourrait indiquer l'émission d'une nouvelle série d'actions privilégiées, ce qui peut avoir un impact sur la structure du capital de la banque. Les actions privilégiées sont souvent utilisées pour renforcer les fonds propres de catégorie 1, conformément aux exigences de Bâle III et aux lignes directrices du BSIF.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer l'émission de cette nouvelle série et évaluer son impact sur les ratios de fonds propres.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -861,19 +838,18 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>L'indicateur "Série 32" a été retiré du tableau des actions privilégiées et autres instruments de capitaux propres au T2 2025, alors qu'il était présent au T1 2025.
-La suppression de cette série peut indiquer le rachat ou l'annulation de cette émission d'actions privilégiées, ce qui pourrait affecter la structure du capital de la banque. Les actions privilégiées sont essentielles pour maintenir les ratios de fonds propres requis par Bâle III.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer la raison de cette suppression et évaluer son impact sur les ratios de fonds propres et la conformité réglementaire.</t>
+La suppression de cette série pourrait indiquer le rachat ou l'annulation de cette série d'actions privilégiées, ce qui peut affecter la composition des fonds propres de la banque. Cela pourrait avoir des implications sur les ratios de fonds propres, notamment ceux liés aux exigences de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier les raisons de cette suppression et évaluer son impact sur la structure du capital.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -914,32 +890,19 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°3 a été supprimée dans le tableau de gestion du capital réglementaire, du ratio de levier et du TLAC. Cette note faisait référence à l'impact du rachat d'actions privilégiées série 32 sur les données au 31 janvier 2025.
-L'absence de cette note dans le rapport actuel pourrait indiquer que l'effet de ce rachat n'est plus pertinent pour la période actuelle ou que l'information a été intégrée ailleurs dans le rapport. Cela pourrait avoir un impact sur la compréhension des ajustements de capital et des ratios de fonds propres, notamment si ces ajustements influencent les calculs de Bâle III ou les exigences du BSIF.
-Il s'agit potentiellement d'une mise à jour structurelle. L'analyste devrait confirmer si l'impact du rachat d'actions a été traité différemment dans le rapport actuel ou s'il est devenu obsolète. Une vérification de la cohérence avec d'autres sections du rapport est recommandée.</t>
+          <t>La note de bas de page n°3 a été supprimée du tableau de gestion du capital réglementaire, du ratio de levier et du TLAC dans le rapport du T2 2025. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
+L'absence de cette note dans le rapport actuel pourrait avoir des implications sur la transparence des informations fournies aux investisseurs et aux régulateurs. Le rachat d'actions privilégiées peut affecter les fonds propres de catégorie 1 et, par conséquent, les ratios de capital réglementaire. Selon les lignes directrices de Bâle III et les exigences du BSIF, toute modification significative des fonds propres doit être clairement divulguée pour assurer la conformité réglementaire et la transparence.
+Il s'agit d'une mise à jour structurelle qui nécessite une vérification pour s'assurer que l'impact du rachat d'actions est toujours correctement reflété dans les données financières présentées. L'analyste devrait confirmer que l'absence de cette note n'entraîne pas de malentendu sur les chiffres rapportés et que les informations pertinentes sont intégrées ailleurs dans le rapport.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T18:59:00.240659+00:00</t>
-        </is>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -980,20 +943,19 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n°4 a été supprimée dans le tableau des exigences réglementaires de ratios des fonds propres, de levier et TLAC au T2 2025. Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
-L'absence de cette note dans le rapport actuel pourrait avoir un impact sur la transparence des informations fournies aux investisseurs et aux régulateurs. En effet, le rachat d'actions privilégiées peut influencer les ratios de fonds propres, et son omission pourrait masquer des variations importantes dans les calculs des ratios prudentiels. Selon les lignes directrices du BSIF, toute modification significative des éléments de fonds propres doit être clairement divulguée pour assurer la conformité avec les exigences de Bâle III.
-Il s'agit d'une mise à jour potentiellement significative qui pourrait indiquer un changement dans la manière dont les événements postérieurs sont pris en compte dans les calculs des ratios. L'analyste devrait confirmer si cette omission est intentionnelle et si elle est conforme aux pratiques de divulgation actuelles. Une investigation plus approfondie est recommandée pour s'assurer que toutes les informations pertinentes sont correctement communiquées.</t>
+          <t>La note de bas de page n-4 a été supprimée dans le tableau des exigences réglementaires de ratios des fonds propres, de levier et TLAC au T2 2025.
+Cette note indiquait que les ratios au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025. La suppression de cette note pourrait indiquer que l'impact de ce rachat n'est plus pertinent pour les ratios actuels ou que l'information a été intégrée ailleurs dans le rapport.
+Il s'agit d'une mise à jour potentiellement significative, car elle pourrait affecter la compréhension des ajustements des ratios de fonds propres. L'analyste devrait confirmer si cette information est redondante ou si elle a été déplacée, et s'assurer que la transparence des divulgations est maintenue.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1018,7 +980,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1029,25 +991,24 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Risque de marché – Acquisitions et cessions</t>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Risque de marché – Acquisitions et cessions" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
-Cet ajout permet de mieux isoler l'impact des acquisitions et cessions sur le risque de marché, ce qui est crucial pour l'évaluation des risques et la planification stratégique. Cela pourrait être lié à des changements dans la structure de l'entreprise ou à des exigences de divulgation accrues.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait s'assurer que cette nouvelle catégorie est justifiée par des changements dans les opérations ou les exigences réglementaires.</t>
+          <t>La note de bas de page n-3 a été ajoutée dans le tableau de gestion du capital au T2 2025.
+Cette note précise que la variation du risque opérationnel est due à l'inclusion de CWB, calculée selon l'approche standardisée. Cela indique un changement dans la composition du risque opérationnel, potentiellement lié à une acquisition ou une intégration stratégique. L'approche standardisée est conforme aux pratiques de Bâle III, ce qui peut influencer les exigences en capital et la gestion des risques.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que l'inclusion de CWB est correctement intégrée dans les calculs de risque et que les divulgations sont cohérentes avec les autres sections du rapport.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1057,22 +1018,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1083,25 +1044,24 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisé conformément à l’approche utilisée par la Banque.</t>
+          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>La note de bas de page n-3 a été ajoutée dans le tableau de gestion du capital au T2 2025.
-Cette note précise que la variation du risque opérationnel est attribuée à l'inclusion de CWB, calculée selon l'approche standardisée. Cela indique un changement potentiel dans la manière dont le risque opérationnel est évalué, ce qui pourrait avoir des implications sur les ratios de capital réglementaire et la conformité aux normes de Bâle III.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette inclusion est cohérente avec les autres sections du rapport et vérifier si elle répond à de nouvelles exigences réglementaires.</t>
+          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet indicateur n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
+Cet ajout reflète une opération spécifique d'émission d'actions ordinaires liée à l'acquisition de CWB. Cela peut avoir un impact significatif sur la structure du capital de la banque, influençant potentiellement les ratios de fonds propres réglementaires tels que le CET1. Les exigences de Bâle III et les lignes directrices du BSIF sur la divulgation des fonds propres pourraient être concernées, car elles nécessitent une transparence accrue sur les événements affectant les fonds propres.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette émission est correctement intégrée dans les calculs des fonds propres et que toutes les implications réglementaires sont bien prises en compte.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1137,37 +1097,24 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
+          <t>Options de remplacement relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet indicateur n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
-Cet ajout reflète une opération spécifique d'acquisition, ce qui peut avoir un impact significatif sur la structure du capital de la banque. Les émissions d'actions ordinaires dans le cadre d'acquisitions peuvent affecter les ratios de fonds propres, qui sont des éléments clés pour le respect des exigences réglementaires telles que Bâle III. Cela peut également influencer la perception des investisseurs et des régulateurs quant à la stratégie de croissance de la banque.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette émission est correctement intégrée dans les calculs des fonds propres et que les impacts sur les ratios réglementaires sont bien documentés.</t>
+          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet indicateur n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
+Cet ajout indique que des options de remplacement ont été émises dans le cadre de l'acquisition de CWB. Cela peut affecter la valorisation des actions et les calculs des fonds propres, influençant potentiellement les ratios de fonds propres réglementaires. Les exigences de Bâle III et les lignes directrices du BSIF sur la divulgation des fonds propres pourraient être concernées, car elles nécessitent une transparence accrue sur les événements affectant les fonds propres.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que ces options sont correctement intégrées dans les calculs des fonds propres et que toutes les implications réglementaires sont bien prises en compte.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T18:58:47.043611+00:00</t>
-        </is>
-      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1192,231 +1139,85 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Options de remplacement relatives à l'acquisition de CWB</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" a été ajouté dans le tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cet indicateur n'était pas présent dans le trimestre précédent terminé le 31 janvier 2025.
-Cet ajout est lié à l'acquisition de CWB et concerne les options de remplacement, ce qui peut avoir des implications sur la valorisation des actions et les droits des actionnaires. Les options de remplacement peuvent modifier la structure du capital et influencer les calculs des fonds propres réglementaires, ce qui est crucial pour le respect des normes de Bâle III et des directives du BSIF.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que ces options sont correctement évaluées et intégrées dans les rapports financiers, et que leur impact sur les ratios de fonds propres est bien compris.</t>
+          <t>La note de bas de page n°2 a été supprimée du tableau des variations des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note indiquait que les données au 31 janvier 2025 prenaient en compte le rachat d’actions privilégiées série 32 effectué le 17 février 2025.
+La suppression de cette note pourrait avoir un impact sur la transparence des informations fournies aux investisseurs et aux régulateurs concernant les événements affectant les fonds propres de la banque. Le rachat d'actions privilégiées peut influencer les ratios de fonds propres réglementaires, tels que le CET1, et doit être correctement divulgué conformément aux exigences de Bâle III et aux lignes directrices du BSIF.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que l'impact de ce rachat est toujours correctement intégré dans les calculs des fonds propres et que toutes les implications réglementaires sont bien prises en compte. Une vérification supplémentaire pourrait être nécessaire pour s'assurer que cette information n'est pas omise ailleurs dans le rapport.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Les données au 31 janvier 2025 tiennent compte du rachat d’actions privilégiées série 32 effectué le 17 février 2025.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>La note de bas de page n°2 a été supprimée du tableau de variation des fonds propres réglementaires pour le semestre terminé le 30 avril 2025. Cette note était présente dans le trimestre précédent terminé le 31 janvier 2025.
-Cette note précisait que les données incluaient le rachat d’actions privilégiées série 32 effectué le 17 février 2025. La suppression de cette note pourrait indiquer que l'événement de rachat n'est plus pertinent pour la période actuelle ou que son impact a été entièrement intégré dans les chiffres présentés. Cela peut avoir des implications sur la transparence des informations fournies aux investisseurs et aux régulateurs, notamment en ce qui concerne la gestion des fonds propres et le respect des exigences de Bâle III.
-Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que l'impact de ce rachat est correctement reflété dans les autres sections du rapport et que la suppression de la note ne compromet pas la compréhension des changements dans les fonds propres.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-23T18:58:52.570557+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Portefeuille d’actifs liquides (1)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Actifs liquides – Au 31 janvier 2025</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>L'indicateur "Actifs liquides – Au 31 janvier 2025" a été retiré du tableau actuel, alors qu'il était présent dans le tableau précédent. Cet indicateur servait à fournir une référence temporelle spécifique pour les actifs liquides à une date antérieure, ce qui est une pratique courante pour contextualiser les données financières dans le temps.
-L'impact de cette suppression est principalement cosmétique, car elle ne modifie pas la méthodologie de calcul ou la présentation des actifs liquides eux-mêmes. Cependant, elle peut affecter la comparaison temporelle directe des données si les utilisateurs du rapport s'appuient sur ces dates pour suivre les tendances historiques. Dans le cadre des exigences réglementaires, cette suppression n'a pas d'incidence directe, car les dates de référence ne sont pas des éléments obligatoires de divulgation selon Bâle III ou les lignes directrices du BSIF.
-Il s'agit d'une mise à jour ordinaire visant probablement à simplifier la présentation du tableau. L'analyste devrait confirmer que les autres dates de référence pertinentes sont toujours présentes et que les utilisateurs du rapport ont accès à toutes les informations nécessaires pour une analyse temporelle complète.</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-23T18:58:56.509411+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Tableau supprimé du trimestre courant.</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-23T18:59:06.366153+00:00</t>
-        </is>
-      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>OUI, le retrait du tableau 'Indicateurs – Banques d’importance systémique mondiale (BISM)' est substantiel. Ce tableau contenait des indicateurs clés tels que l'activité transfrontière, la taille, l'interdépendance, la substituabilité/infrastructure financière et la complexité. Ces indicateurs sont cruciaux pour évaluer l'importance systémique d'une banque. Leur suppression modifie la structure du rapport et la divulgation des risques associés aux BISM. Cela représente un changement significatif dans la manière dont la banque communique ses risques systémiques, ce qui est pertinent pour les thèmes AMF de DIVULGATION_RETRAIT et STRUCTURE_RAPPORT.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:M14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11T14:00:39.880382+00:00</t>
+          <t>2026-06-23T15:19:10.056827+00:00</t>
         </is>
       </c>
     </row>
@@ -793,16 +793,8 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-11T14:00:40.430625+00:00</t>
-        </is>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">

--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -581,8 +581,16 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T19:42:33.142071+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -741,7 +749,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T15:19:10.056827+00:00</t>
+          <t>2026-06-24T19:42:25.262918+00:00</t>
         </is>
       </c>
     </row>
@@ -793,8 +801,16 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T19:42:55.559989+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1048,8 +1064,16 @@
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T19:42:57.806568+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">

--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -581,16 +581,8 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-24T19:42:33.142071+00:00</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -749,7 +741,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T19:42:25.262918+00:00</t>
+          <t>2026-06-25T15:17:25.021843+00:00</t>
         </is>
       </c>
     </row>
@@ -808,7 +800,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T19:42:55.559989+00:00</t>
+          <t>2026-06-25T15:19:11.366220+00:00</t>
         </is>
       </c>
     </row>
@@ -911,8 +903,16 @@
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T15:19:18.162270+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -962,8 +962,16 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T15:19:19.751155+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1071,7 +1079,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T19:42:57.806568+00:00</t>
+          <t>2026-06-25T15:17:57.233229+00:00</t>
         </is>
       </c>
     </row>

--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Page T1</t>
+          <t>Page (trimestre précédent)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Page T2</t>
+          <t>Page (trimestre courant)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T1</t>
+          <t>Libellé (trimestre précédent)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T2</t>
+          <t>Libellé (trimestre courant)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -581,8 +581,16 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T03:59:55.662559+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -741,7 +749,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:17:25.021843+00:00</t>
+          <t>2026-07-28T03:57:01.038922+00:00</t>
         </is>
       </c>
     </row>
@@ -793,16 +801,8 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25T15:19:11.366220+00:00</t>
-        </is>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:19:18.162270+00:00</t>
+          <t>2026-07-28T03:59:45.951819+00:00</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:19:19.751155+00:00</t>
+          <t>2026-07-28T03:59:28.404628+00:00</t>
         </is>
       </c>
     </row>
@@ -1072,16 +1072,8 @@
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25T15:17:57.233229+00:00</t>
-        </is>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">

--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -581,16 +581,8 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28T03:59:55.662559+00:00</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -749,7 +741,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28T03:57:01.038922+00:00</t>
+          <t>2026-07-30T18:40:54.988811+00:00</t>
         </is>
       </c>
     </row>
@@ -903,16 +895,8 @@
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28T03:59:45.951819+00:00</t>
-        </is>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -962,16 +946,8 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28T03:59:28.404628+00:00</t>
-        </is>
-      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">

--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -734,16 +734,8 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-30T18:40:54.988811+00:00</t>
-        </is>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1197,8 +1189,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07T05:53:34.016117+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M14"/>
